--- a/Lista Maestra SG-SST Maximia.xlsx
+++ b/Lista Maestra SG-SST Maximia.xlsx
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1724,37 +1724,37 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>FR-01</t>
+          <t>FR-25-07</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Registro e Investigación de Incidentes</t>
+          <t>Asistencia a Capacitación</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Maximia (oficiales)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.2 / 7.3</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>PR-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -1774,27 +1774,27 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>FR-02</t>
+          <t>FR-27-05</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Registro de Asistencia a Capacitación</t>
+          <t>Plan Anual de Capacitaciones</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Maximia (oficiales)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PR-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1824,37 +1824,37 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>FR-85-02</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Evaluación de Efectividad de Capacitación</t>
+          <t>Plan de Acción</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Maximia (oficiales)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>7.2 / 7.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>PR-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -1874,17 +1874,17 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>FR-04</t>
+          <t>FR-107-01</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Matriz de Requisitos Legales</t>
+          <t>Control de Higiene y Seguridad – Lista de Chequeo HyS</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Maximia (oficiales)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PR-05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Vigente</t>
+          <t>3 años</t>
         </is>
       </c>
     </row>
@@ -1924,17 +1924,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>FR-109-01</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Registro de Entrega de EPP</t>
+          <t>Informe Técnico de Investigación de Accidentes e Incidentes</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Maximia (oficiales)</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1944,22 +1944,22 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>PR-10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Responsable SST / Supervisor</t>
+          <t>Responsable SST</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>FR-06</t>
+          <t>FR-113-01</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Inventario de Sustancias Químicas</t>
+          <t>Indicadores SST – Tablero Mensual</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Formularios SST</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>9.1 / 9.1.1</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PR-10</t>
+          <t>FR-11 (anterior)</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>Permanente</t>
+          <t>5 años</t>
         </is>
       </c>
     </row>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>FR-07</t>
+          <t>FR-114-01</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Registro de Ingreso de Contratistas</t>
+          <t>Registro de No Conformidades</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Formularios SST</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>8.1.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>PR-10</t>
+          <t>FR-01 (anterior)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Responsable SST / Recepción</t>
+          <t>Responsable SST</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>3 años</t>
+          <t>5 años</t>
         </is>
       </c>
     </row>
@@ -2074,17 +2074,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>FR-08</t>
+          <t>FR-115-01</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Inspección de Condiciones de Trabajo</t>
+          <t>Formulario de Investigación de Incidentes</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>FR - Formularios</t>
+          <t>FR - Formularios SST</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -2094,202 +2094,515 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Mar-2026</t>
+          <t>May-2026</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PR-10 / PR-12</t>
+          <t>FR-01 (anterior)</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Supervisor / SST</t>
+          <t>Responsable SST</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
+          <t>5 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>FR-117-01</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Registro de Entrega de EPP</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>FR-05 (anterior)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Responsable SST</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>FR-118-01</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Acta de Revisión por la Dirección</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Gerencia / SST</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>FR-119-01</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Inventario de Sustancias Químicas</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>FR-06 (anterior)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Responsable SST</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>Permanente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>FR-120-01</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Registro de Ingreso de Contratistas</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>8.1.4</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>FR-07 (anterior)</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Responsable SST</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
           <t>3 años</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>FR-09</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>FR-121-01</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Registro de Simulacro de Emergencia</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>FR - Formularios</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Mar-2026</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>PR-11</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>FR-09 (anterior)</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Responsable SST</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>5 años</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B35" s="14" t="n"/>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
-      <c r="H35" s="14" t="n"/>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="15" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>FR-11</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Tablero de Indicadores SST</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>FR - Formularios</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>FR-122-01</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Informe de Auditoría Interna SST</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Mar-2026</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>PR-12</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Auditor / Resp. SST</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>5 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>FR-123-01</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Formulario de Gestión del Cambio SST</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>8.1.3</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Responsable SST</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>5 años</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>FR-12</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="n"/>
-      <c r="G37" s="14" t="n"/>
-      <c r="H37" s="14" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>5 años</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Los documentos anteriores (originales) se conservan en la carpeta Anexos/ sin modificaciones. | Próxima revisión: Marzo 2027</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
-      <c r="G38" s="14" t="n"/>
-      <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="15" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>NOTA (Abr-2026):</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>Los procedimientos PR-01, PR-03, PR-04, PR-11 y PR-14 fueron actualizados a Versión 02 (Abril 2026) por incorporación de la Enmienda ISO 45001:2018/Amd 1:2024 — Climate action changes.</t>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>FR-124-01</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Permiso de Trabajo para Tareas de Riesgo</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Responsable SST</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>3 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>FR-125-01</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Listado de Contratistas Habilitados</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>FR - Formularios SST</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>May-2026</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>8.1.4</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Responsable SST</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Documentos anteriores conservados en Anexos/ sin modificaciones. | Próxima revisión: Mayo 2027</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="15" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>NOTA (May-2026):</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>NOTA (May-2026): Lista Maestra actualizada a v03. FRs oficiales de Maximia registrados con sus códigos reales. FRs del SG-SST creados con numeración interna (FR-113 a FR-125) — números definitivos pendientes de confirmación.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:J4"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A44:J44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3038,12 +3351,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>FR-01 a FR-12</t>
+          <t>FR-25-07 a FR-125-01</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3367,7 @@
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
     </row>
@@ -3204,7 +3517,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>FR-01 a FR-12</t>
+          <t>FR-25-07 a FR-125-01</t>
         </is>
       </c>
     </row>
@@ -3318,291 +3631,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010022E641D985E02047BE4A10568660F6CD" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="42d7c85178e2dcea15d07bb1687c69a3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8d6af3c6-6506-406f-906a-363a197505cb" xmlns:ns3="bb2b36ed-bee3-4b57-9f16-23d26e905edb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6e4823d1a1bcfba0042ce6f85749729" ns2:_="" ns3:_="">
-    <xsd:import namespace="8d6af3c6-6506-406f-906a-363a197505cb"/>
-    <xsd:import namespace="bb2b36ed-bee3-4b57-9f16-23d26e905edb"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8d6af3c6-6506-406f-906a-363a197505cb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="10" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="13" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7353464e-1a1a-4dd7-9163-d2497400ae66" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bb2b36ed-bee3-4b57-9f16-23d26e905edb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{098e5fb6-7d21-4832-a6f2-5c3c749cbddc}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="bb2b36ed-bee3-4b57-9f16-23d26e905edb">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bb2b36ed-bee3-4b57-9f16-23d26e905edb" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8d6af3c6-6506-406f-906a-363a197505cb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2F2369E-DB69-4B25-A863-FF56924AC3FE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CF2D522-7DB9-4352-B51B-0488760D46A6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21EBD861-48FD-4CE8-B486-DC32DB33AC43}"/>
 </file>